--- a/问题4/口径对照_读法与结算与调整规则.xlsx
+++ b/问题4/口径对照_读法与结算与调整规则.xlsx
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="C10" s="1" t="n">
-        <v>20189815.7495</v>
+        <v>20238798.2446</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C11" s="1" t="n">
-        <v>19730598.4206</v>
+        <v>19940609.8523</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -723,11 +723,11 @@
         </is>
       </c>
       <c r="E11" s="1" t="n">
-        <v>-2.2745</v>
+        <v>-1.4734</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>漏计当天第 1 段（0:00–0:10）合计 459217.3289 kWh，全天购电量偏差</t>
+          <t>漏计当天第 1 段（0:00–0:10）合计 298188.3923 kWh，全天购电量偏差</t>
         </is>
       </c>
     </row>
